--- a/8_Other_diagnostics.xlsx
+++ b/8_Other_diagnostics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://univpecs-my.sharepoint.com/personal/d4ykh4_tr_pte_hu/Documents/Dokumentumok/PhD/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D4YKH4\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01E980E8-4C3E-41CA-9EFB-318A1C545250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF5E0FF-BF6D-4018-984F-F28F509A89F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="741" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="741" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Other Diagnostics" sheetId="1" r:id="rId1"/>
@@ -218,7 +218,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,9 +239,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="238"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -253,12 +256,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59996337778862885"/>
+        <fgColor rgb="FFB8CCE4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -281,41 +284,73 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFB8CCE4"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -625,621 +660,648 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="23.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="72.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="82.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="1" width="21.765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="85" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.15234375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.15234375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="2" t="s">
+      <c r="E2" s="11"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="12"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="2" t="s">
+      <c r="E3" s="10"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="12"/>
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="2" t="s">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="12"/>
+      <c r="B5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="3"/>
+      <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" s="12"/>
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="3"/>
+      <c r="E6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" s="12"/>
+      <c r="B7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
+      <c r="D7" s="3"/>
+      <c r="E7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" s="12"/>
+      <c r="B8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
+      <c r="D8" s="3"/>
+      <c r="E8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" s="12"/>
+      <c r="B9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="4" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="12"/>
+      <c r="B10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="2" t="s">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="12"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="4" t="s">
+      <c r="E11" s="10"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="12"/>
+      <c r="B12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="2" t="s">
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="2" t="s">
+      <c r="E13" s="12"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="2" t="s">
+      <c r="E14" s="12"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="2" t="s">
+      <c r="E15" s="12"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="2" t="s">
+      <c r="E16" s="12"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="2" t="s">
+      <c r="E17" s="12"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="2" t="s">
+      <c r="E18" s="12"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="2" t="s">
+      <c r="E19" s="12"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="2" t="s">
+      <c r="E20" s="12"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="2" t="s">
+      <c r="E21" s="12"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="2" t="s">
+      <c r="E22" s="12"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="2" t="s">
+      <c r="E23" s="12"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="2" t="s">
+      <c r="E24" s="12"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="12"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="4" t="s">
+      <c r="E25" s="10"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="12"/>
+      <c r="B26" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="2" t="s">
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="E27" s="10"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="2" t="s">
+      <c r="E28" s="11"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="12"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
-      <c r="B30" s="4" t="s">
+      <c r="E29" s="10"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="12"/>
+      <c r="B30" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="2" t="s">
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="12"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-      <c r="B32" s="4" t="s">
+      <c r="E31" s="10"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="12"/>
+      <c r="B32" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="2" t="s">
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="2" t="s">
+      <c r="E33" s="12"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="2" t="s">
+      <c r="E34" s="12"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="12"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
-      <c r="B36" s="2" t="s">
+      <c r="E35" s="10"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="10"/>
+      <c r="B36" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2" t="s">
+      <c r="D36" s="3"/>
+      <c r="E36" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="5"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="2" t="s">
+      <c r="E37" s="11"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="12"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
-      <c r="B39" s="2" t="s">
+      <c r="E38" s="10"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="12"/>
+      <c r="B39" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3" t="s">
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="12"/>
+      <c r="B40" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3" t="s">
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" s="10"/>
+      <c r="B41" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3" t="s">
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B42" s="8"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B43" s="9"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B45" s="11"/>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42" s="5"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" s="5"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44" s="5"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A45" s="5"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B37:B38"/>
     <mergeCell ref="A2:A27"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="E2:E3"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="B12:B25"/>
     <mergeCell ref="A28:A36"/>
     <mergeCell ref="C32:C35"/>
     <mergeCell ref="E26:E27"/>
+    <mergeCell ref="E32:E35"/>
     <mergeCell ref="B30:B31"/>
-    <mergeCell ref="E32:E35"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C12:C25"/>
     <mergeCell ref="C37:C38"/>
     <mergeCell ref="E37:E38"/>
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="A37:A41"/>
+    <mergeCell ref="B32:B35"/>
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C10:C11"/>
@@ -1247,9 +1309,10 @@
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="E28:E29"/>
     <mergeCell ref="E12:E25"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B10:B11"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
